--- a/data/rules/postNormalization.xlsx
+++ b/data/rules/postNormalization.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mac/Desktop/VV_Python_Project/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mac/Desktop/VV_Python_Project/data/rules/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{206A6160-8D8E-0345-B2DE-FA53423188E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{460C0AB3-9783-1349-A5EA-C5BC02A35DB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="360" yWindow="560" windowWidth="26400" windowHeight="11600" xr2:uid="{B74B3832-BD25-7041-B5F7-B1DA2806F8F0}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="20">
   <si>
     <t>priority</t>
   </si>
@@ -92,6 +92,9 @@
   </si>
   <si>
     <t>comments[].type</t>
+  </si>
+  <si>
+    <t>DEDUPLICATE_ALL_ARRAYS</t>
   </si>
 </sst>
 </file>
@@ -468,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB3F5EBA-8684-4C46-B211-385CBAE6C770}">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
@@ -579,6 +582,14 @@
         <v>17</v>
       </c>
     </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>100</v>
+      </c>
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
